--- a/docs/templates/CAMRI_ARG_Input_Template.xlsx
+++ b/docs/templates/CAMRI_ARG_Input_Template.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CAMRI ARG Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAMRI ARG Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -505,6 +505,16 @@
           <t>copies/mL</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>copies/mL</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>copies/mL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -539,42 +549,52 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>blaKPC</t>
+          <t>AY456_qepA</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>blaCTX_M</t>
+          <t>AY461_qnrS2</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>vanA</t>
+          <t>AY466_MCR-1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>blaNDM</t>
+          <t>AY134_blaCTX-M_5</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>blaSHV</t>
+          <t>AY152_blaNDM</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>tetO</t>
+          <t>AY104_blaSHV_1</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>tetM</t>
+          <t>AY601_blaOXA48</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>qnrA</t>
+          <t>AY153_blaKPC_2</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>AY8_AAC6-Ib_1</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>AY32_floR_1</t>
         </is>
       </c>
     </row>
